--- a/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
+++ b/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C15N\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\autopeak\jobs13C15N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A017B8AA-B0F8-4DD0-A5C2-12AA7A57D98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7391CC-64AF-4BEF-9A22-B2D423E68DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="165">
   <si>
     <t>inclusion</t>
   </si>
@@ -62,27 +62,12 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240603-Glc-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;ctrl-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;glc-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240618-Arg-Cys-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;cys-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;arg-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240712-Trp-Acet-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;trp-</t>
-  </si>
-  <si>
     <t>mzxml;neg;acet-;M19</t>
   </si>
   <si>
@@ -92,57 +77,24 @@
     <t>mzxml;neg;acet-;M28</t>
   </si>
   <si>
-    <t>mzxml;neg;cit-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240825-Jenna-13C-Thr-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;thr-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240909-Val-Isoleu-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;ile-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;val-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240923-Lys-Leu-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;lys-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;leu-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20241016-Pro-Lin-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;pro-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;lin-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20241104-Inosine-Uridine-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;ino-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;uri-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20241227-13C-gly-tracing\480K</t>
   </si>
   <si>
-    <t>mzxml;T</t>
-  </si>
-  <si>
     <t>M41;M43;AIF;-mz-</t>
   </si>
   <si>
@@ -161,9 +113,6 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20250505-13C-Taurine-ED</t>
   </si>
   <si>
-    <t>mzxml;neg;Tau</t>
-  </si>
-  <si>
     <t>M4;M8</t>
   </si>
   <si>
@@ -173,36 +122,12 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20250518-Vitamin-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;biotin</t>
-  </si>
-  <si>
-    <t>mzxml;neg;thia</t>
-  </si>
-  <si>
-    <t>mzxml;neg;rib</t>
-  </si>
-  <si>
-    <t>mzxml;neg;Pantothenate</t>
-  </si>
-  <si>
-    <t>mzxml;neg;control</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20250725-Fructose-palmt-oleat-tracing</t>
   </si>
   <si>
     <t>mzxml;neg;palm</t>
   </si>
   <si>
-    <t>mzxml;neg;oleat</t>
-  </si>
-  <si>
-    <t>mzxml;neg;fruc;30min</t>
-  </si>
-  <si>
-    <t>mzxml;neg;fruc;60min</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\Michael_M\20250721_mevalonolactone</t>
   </si>
   <si>
@@ -245,21 +170,6 @@
     <t>T03_Met</t>
   </si>
   <si>
-    <t>T04_Ctrl-Glc</t>
-  </si>
-  <si>
-    <t>T05_glc</t>
-  </si>
-  <si>
-    <t>T06_Cys</t>
-  </si>
-  <si>
-    <t>T07_Arg</t>
-  </si>
-  <si>
-    <t>T08_Trp</t>
-  </si>
-  <si>
     <t>T09_Ace1</t>
   </si>
   <si>
@@ -269,75 +179,12 @@
     <t>T11_Cit</t>
   </si>
   <si>
-    <t>T12_Thr</t>
-  </si>
-  <si>
-    <t>T13_Ile</t>
-  </si>
-  <si>
-    <t>T14_Val</t>
-  </si>
-  <si>
-    <t>T15_Lys</t>
-  </si>
-  <si>
-    <t>T16_Leu</t>
-  </si>
-  <si>
-    <t>T17_Pro</t>
-  </si>
-  <si>
-    <t>T18_Lin</t>
-  </si>
-  <si>
-    <t>T19_Ino</t>
-  </si>
-  <si>
-    <t>T20_Uri</t>
-  </si>
-  <si>
-    <t>T21_Gly</t>
-  </si>
-  <si>
-    <t>T22_Ctrl-Gly</t>
-  </si>
-  <si>
-    <t>T23_Vpan1</t>
-  </si>
-  <si>
-    <t>T24_Tau</t>
-  </si>
-  <si>
-    <t>T25_Ctrl-Tau</t>
-  </si>
-  <si>
-    <t>T26_Vbio</t>
-  </si>
-  <si>
-    <t>T27_Vthia</t>
-  </si>
-  <si>
-    <t>T28_Vrib</t>
-  </si>
-  <si>
     <t>T29_Vpan2</t>
   </si>
   <si>
-    <t>T30_Ctrl-V</t>
-  </si>
-  <si>
     <t>T31_palmt</t>
   </si>
   <si>
-    <t>T32_oleat</t>
-  </si>
-  <si>
-    <t>T33_Fruc_30min</t>
-  </si>
-  <si>
-    <t>T34_Fruc_60min</t>
-  </si>
-  <si>
     <t>T35_meval_serum</t>
   </si>
   <si>
@@ -366,13 +213,334 @@
   </si>
   <si>
     <t>folder</t>
+  </si>
+  <si>
+    <t>mzxml;neg;ctrl-;M7</t>
+  </si>
+  <si>
+    <t>mzxml;neg;ctrl-;M8</t>
+  </si>
+  <si>
+    <t>mzxml;neg;glc-;M10</t>
+  </si>
+  <si>
+    <t>mzxml;neg;glc-;M11</t>
+  </si>
+  <si>
+    <t>mzxml;neg;cys-;M12</t>
+  </si>
+  <si>
+    <t>mzxml;neg;cys-;M13</t>
+  </si>
+  <si>
+    <t>T04_Ctrl-Glc1</t>
+  </si>
+  <si>
+    <t>T04_Ctrl-Glc2</t>
+  </si>
+  <si>
+    <t>T05_glc1</t>
+  </si>
+  <si>
+    <t>T05_glc2</t>
+  </si>
+  <si>
+    <t>T06_Cys1</t>
+  </si>
+  <si>
+    <t>T06_Cys2</t>
+  </si>
+  <si>
+    <t>T07_Arg1</t>
+  </si>
+  <si>
+    <t>T07_Arg2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;arg-;M14</t>
+  </si>
+  <si>
+    <t>mzxml;neg;arg-;M15</t>
+  </si>
+  <si>
+    <t>T08_Trp1</t>
+  </si>
+  <si>
+    <t>T08_Trp2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;trp-;M16</t>
+  </si>
+  <si>
+    <t>mzxml;neg;trp-;M17</t>
+  </si>
+  <si>
+    <t>mzxml;neg;cit-;M29</t>
+  </si>
+  <si>
+    <t>T12_Thr1</t>
+  </si>
+  <si>
+    <t>T12_Thr2</t>
+  </si>
+  <si>
+    <t>T12_Thr3</t>
+  </si>
+  <si>
+    <t>mzxml;neg;thr-;M453</t>
+  </si>
+  <si>
+    <t>mzxml;neg;thr-;M454</t>
+  </si>
+  <si>
+    <t>mzxml;neg;thr-;M455</t>
+  </si>
+  <si>
+    <t>T13_Ile1</t>
+  </si>
+  <si>
+    <t>T13_Ile2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;ile-;M24</t>
+  </si>
+  <si>
+    <t>mzxml;neg;ile-;M25</t>
+  </si>
+  <si>
+    <t>T14_Val1</t>
+  </si>
+  <si>
+    <t>T14_Val2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;val-;M26</t>
+  </si>
+  <si>
+    <t>mzxml;neg;lys-;M20</t>
+  </si>
+  <si>
+    <t>mzxml;neg;lys-;M21</t>
+  </si>
+  <si>
+    <t>mzxml;neg;leu-;M22</t>
+  </si>
+  <si>
+    <t>mzxml;neg;leu-;M23</t>
+  </si>
+  <si>
+    <t>T15_Lys1</t>
+  </si>
+  <si>
+    <t>T15_Lys2</t>
+  </si>
+  <si>
+    <t>T16_Leu1</t>
+  </si>
+  <si>
+    <t>T16_Leu2</t>
+  </si>
+  <si>
+    <t>T17_Pro1</t>
+  </si>
+  <si>
+    <t>T17_Pro2</t>
+  </si>
+  <si>
+    <t>T18_Lin1</t>
+  </si>
+  <si>
+    <t>T18_Lin2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;pro-;M30</t>
+  </si>
+  <si>
+    <t>mzxml;neg;pro-;M31</t>
+  </si>
+  <si>
+    <t>mzxml;neg;lin-;M32</t>
+  </si>
+  <si>
+    <t>mzxml;neg;lin-;M33</t>
+  </si>
+  <si>
+    <t>mzxml;neg;ino-;M34</t>
+  </si>
+  <si>
+    <t>mzxml;neg;ino-;M35</t>
+  </si>
+  <si>
+    <t>mzxml;neg;uri-;M37</t>
+  </si>
+  <si>
+    <t>T19_Ino1</t>
+  </si>
+  <si>
+    <t>T19_Ino2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;uri-;M36</t>
+  </si>
+  <si>
+    <t>T20_Uri1</t>
+  </si>
+  <si>
+    <t>T20_Uri2</t>
+  </si>
+  <si>
+    <t>T21_Gly1</t>
+  </si>
+  <si>
+    <t>T21_Gly2</t>
+  </si>
+  <si>
+    <t>mzxml;T;M39</t>
+  </si>
+  <si>
+    <t>mzxml;T;M40</t>
+  </si>
+  <si>
+    <t>mzxml;T;M41</t>
+  </si>
+  <si>
+    <t>mzxml;T;M43</t>
+  </si>
+  <si>
+    <t>T22_Ctrl-Gly1</t>
+  </si>
+  <si>
+    <t>T22_Ctrl-Gly2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;Tau;M2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;Tau;M7</t>
+  </si>
+  <si>
+    <t>mzxml;neg;Tau;M4</t>
+  </si>
+  <si>
+    <t>mzxml;neg;Tau;M8</t>
+  </si>
+  <si>
+    <t>T24_Tau1</t>
+  </si>
+  <si>
+    <t>T24_Tau2</t>
+  </si>
+  <si>
+    <t>T25_Ctrl-Tau1</t>
+  </si>
+  <si>
+    <t>T25_Ctrl-Tau2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;biotin;M44</t>
+  </si>
+  <si>
+    <t>T26_Vbio1</t>
+  </si>
+  <si>
+    <t>T26_Vbio2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;biotin;M45</t>
+  </si>
+  <si>
+    <t>T27_Vthia1</t>
+  </si>
+  <si>
+    <t>T27_Vthia2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;thia;M46</t>
+  </si>
+  <si>
+    <t>mzxml;neg;thia;M47</t>
+  </si>
+  <si>
+    <t>T28_Vrib1</t>
+  </si>
+  <si>
+    <t>T28_Vrib2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;rib;M48</t>
+  </si>
+  <si>
+    <t>mzxml;neg;rib;M49</t>
+  </si>
+  <si>
+    <t>T29_Vpan1</t>
+  </si>
+  <si>
+    <t>mzxml;neg;Pantothenate;M50</t>
+  </si>
+  <si>
+    <t>mzxml;neg;Pantothenate;M51</t>
+  </si>
+  <si>
+    <t>T23_VpanT</t>
+  </si>
+  <si>
+    <t>T30_Ctrl-V1</t>
+  </si>
+  <si>
+    <t>T30_Ctrl-V2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;control;M52</t>
+  </si>
+  <si>
+    <t>mzxml;neg;control;M53</t>
+  </si>
+  <si>
+    <t>T32_oleat1</t>
+  </si>
+  <si>
+    <t>T32_oleat2</t>
+  </si>
+  <si>
+    <t>T33_Fruc_30min1</t>
+  </si>
+  <si>
+    <t>T33_Fruc_30min2</t>
+  </si>
+  <si>
+    <t>T34_Fruc_60min1</t>
+  </si>
+  <si>
+    <t>T34_Fruc_60min2</t>
+  </si>
+  <si>
+    <t>mzxml;neg;fruc;30min;M58</t>
+  </si>
+  <si>
+    <t>mzxml;neg;fruc;30min;M59</t>
+  </si>
+  <si>
+    <t>mzxml;neg;fruc;60min;M60</t>
+  </si>
+  <si>
+    <t>mzxml;neg;fruc;60min;M61</t>
+  </si>
+  <si>
+    <t>mzxml;neg;oleat;M56</t>
+  </si>
+  <si>
+    <t>mzxml;neg;oleat;M57</t>
+  </si>
+  <si>
+    <t>mzxml;neg;palm;M55</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +557,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -414,9 +590,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -751,10 +929,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10984C3E-EACA-4DD3-AD3A-E289D3D20B1E}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.5703125" customWidth="1"/>
+    <col min="1" max="1" width="85.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -764,13 +942,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -784,10 +962,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -798,10 +976,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -812,10 +990,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -826,13 +1004,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
+        <v>56</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -840,550 +1018,941 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
+        <v>56</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
+        <v>56</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
         <v>75</v>
       </c>
-      <c r="C12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
         <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>120</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="B42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>23</v>
       </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>26</v>
       </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="B67" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" t="s">
+        <v>56</v>
+      </c>
+      <c r="D67" t="s">
         <v>33</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E67" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B68" t="s">
+        <v>53</v>
+      </c>
+      <c r="C68" t="s">
+        <v>56</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E68" t="s">
         <v>37</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" t="s">
+        <v>56</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E41" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C42" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" s="1"/>
+      <c r="F69" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
+++ b/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\autopeak\jobs13C15N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7391CC-64AF-4BEF-9A22-B2D423E68DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACD9FFF-5629-486E-86D5-B0BABCDC01AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="174">
   <si>
     <t>inclusion</t>
   </si>
@@ -125,9 +125,6 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20250725-Fructose-palmt-oleat-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;palm</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\Michael_M\20250721_mevalonolactone</t>
   </si>
   <si>
@@ -137,21 +134,12 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20251111-Phe-Gln-Palm-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;phe</t>
-  </si>
-  <si>
-    <t>mzxml;neg;gln</t>
-  </si>
-  <si>
     <t>M62;M63</t>
   </si>
   <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20260118-Acetate-Mevalonate-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg</t>
-  </si>
-  <si>
     <t>M71;M72;M73;blank</t>
   </si>
   <si>
@@ -534,6 +522,45 @@
   </si>
   <si>
     <t>mzxml;neg;palm;M55</t>
+  </si>
+  <si>
+    <t>blank</t>
+  </si>
+  <si>
+    <t>mzxml;neg;gln;M66</t>
+  </si>
+  <si>
+    <t>mzxml;neg;gln;M67</t>
+  </si>
+  <si>
+    <t>mzxml;neg;palm;M64</t>
+  </si>
+  <si>
+    <t>mzxml;neg;palm;M65</t>
+  </si>
+  <si>
+    <t>mzxml;neg;phe;M60</t>
+  </si>
+  <si>
+    <t>mzxml;neg;phe;M61</t>
+  </si>
+  <si>
+    <t>mzxml;neg;M71</t>
+  </si>
+  <si>
+    <t>mzxml;neg;M72</t>
+  </si>
+  <si>
+    <t>mzxml;neg;M73</t>
+  </si>
+  <si>
+    <t>mzxml;neg;M68</t>
+  </si>
+  <si>
+    <t>mzxml;neg;M69</t>
+  </si>
+  <si>
+    <t>mzxml;neg;M70</t>
   </si>
 </sst>
 </file>
@@ -929,26 +956,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10984C3E-EACA-4DD3-AD3A-E289D3D20B1E}">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="85.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.140625" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -962,10 +989,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -976,10 +1003,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -990,10 +1017,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1004,13 +1031,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1018,13 +1045,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1032,13 +1059,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1046,13 +1073,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1060,13 +1087,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1074,13 +1101,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1088,13 +1115,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1102,13 +1129,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1116,13 +1143,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1130,13 +1157,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1144,10 +1171,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
@@ -1158,10 +1185,10 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1172,13 +1199,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1186,13 +1213,13 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,13 +1227,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,13 +1241,13 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1228,13 +1255,13 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1242,13 +1269,13 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1256,13 +1283,13 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1270,13 +1297,13 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,13 +1311,13 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1298,13 +1325,13 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1312,13 +1339,13 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,13 +1353,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,13 +1367,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
         <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,13 +1381,13 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
         <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,13 +1395,13 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" t="s">
         <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,13 +1409,13 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" t="s">
         <v>103</v>
-      </c>
-      <c r="C32" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1396,13 +1423,13 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1410,13 +1437,13 @@
         <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1424,13 +1451,13 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1438,13 +1465,13 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1452,13 +1479,13 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E37" t="s">
         <v>18</v>
@@ -1469,13 +1496,13 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E38" t="s">
         <v>18</v>
@@ -1486,13 +1513,13 @@
         <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -1503,13 +1530,13 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -1520,10 +1547,10 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D41" t="s">
         <v>21</v>
@@ -1537,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
         <v>24</v>
@@ -1554,13 +1581,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -1571,13 +1598,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
@@ -1588,13 +1615,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
@@ -1605,13 +1632,13 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D46" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1619,13 +1646,13 @@
         <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1633,322 +1660,448 @@
         <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D51" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>27</v>
       </c>
       <c r="B59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C59" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" t="s">
         <v>154</v>
       </c>
-      <c r="C59" t="s">
-        <v>56</v>
-      </c>
-      <c r="D59" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>27</v>
       </c>
       <c r="B60" t="s">
+        <v>151</v>
+      </c>
+      <c r="C60" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" t="s">
         <v>155</v>
       </c>
-      <c r="C60" t="s">
-        <v>56</v>
-      </c>
-      <c r="D60" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>27</v>
       </c>
       <c r="B61" t="s">
+        <v>152</v>
+      </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" t="s">
         <v>156</v>
       </c>
-      <c r="C61" t="s">
-        <v>56</v>
-      </c>
-      <c r="D61" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>27</v>
       </c>
       <c r="B62" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" t="s">
         <v>157</v>
       </c>
-      <c r="C62" t="s">
-        <v>56</v>
-      </c>
-      <c r="D62" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C63" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D63" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D64" t="s">
         <v>21</v>
       </c>
+      <c r="E64" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C65" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D65" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C66" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D66" t="s">
-        <v>28</v>
-      </c>
-      <c r="E66" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C67" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D67" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C68" t="s">
-        <v>56</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
+      </c>
+      <c r="D68" t="s">
+        <v>165</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
-      </c>
-      <c r="F68" s="1"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F69" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="D69" t="s">
+        <v>162</v>
+      </c>
+      <c r="E69" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>30</v>
+      </c>
+      <c r="B70" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" t="s">
+        <v>52</v>
+      </c>
+      <c r="D70" t="s">
+        <v>163</v>
+      </c>
+      <c r="E70" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>32</v>
+      </c>
+      <c r="B71" t="s">
+        <v>49</v>
+      </c>
+      <c r="C71" t="s">
+        <v>52</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E71" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72" t="s">
+        <v>52</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E72" t="s">
+        <v>33</v>
+      </c>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>32</v>
+      </c>
+      <c r="B73" t="s">
+        <v>49</v>
+      </c>
+      <c r="C73" t="s">
+        <v>52</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E73" t="s">
+        <v>33</v>
+      </c>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>32</v>
+      </c>
+      <c r="B75" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75" s="1"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>32</v>
+      </c>
+      <c r="B76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
+++ b/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\autopeak\jobs13C15N\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C15N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACD9FFF-5629-486E-86D5-B0BABCDC01AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81185DA9-D603-45A1-8190-C06A85922219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="181">
   <si>
     <t>inclusion</t>
   </si>
@@ -182,12 +182,6 @@
     <t>T37_phe</t>
   </si>
   <si>
-    <t>T38_palmt</t>
-  </si>
-  <si>
-    <t>T39_gln</t>
-  </si>
-  <si>
     <t>T40_meval_C2</t>
   </si>
   <si>
@@ -561,6 +555,33 @@
   </si>
   <si>
     <t>mzxml;neg;M70</t>
+  </si>
+  <si>
+    <t>T37_phe2</t>
+  </si>
+  <si>
+    <t>T38_palmt1</t>
+  </si>
+  <si>
+    <t>T38_palmt2</t>
+  </si>
+  <si>
+    <t>T39_gln1</t>
+  </si>
+  <si>
+    <t>T39_gln2</t>
+  </si>
+  <si>
+    <t>T40_meval_C1</t>
+  </si>
+  <si>
+    <t>T40_meval_C3</t>
+  </si>
+  <si>
+    <t>T41_Ace1</t>
+  </si>
+  <si>
+    <t>T41_Ace2</t>
   </si>
 </sst>
 </file>
@@ -617,11 +638,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,13 +989,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -992,7 +1012,7 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1006,7 +1026,7 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -1020,7 +1040,7 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1031,13 +1051,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1045,13 +1065,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1059,13 +1079,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,13 +1093,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1087,13 +1107,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1101,13 +1121,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1115,13 +1135,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
         <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1129,41 +1149,41 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
         <v>67</v>
       </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
         <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1174,7 +1194,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
@@ -1188,24 +1208,24 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>10</v>
       </c>
       <c r="B17" t="s">
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1213,13 +1233,13 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,13 +1247,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1241,13 +1261,13 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,13 +1275,13 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
         <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1269,13 +1289,13 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
         <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,13 +1303,13 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" t="s">
         <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1297,13 +1317,13 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1311,13 +1331,13 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,13 +1345,13 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1339,13 +1359,13 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1353,13 +1373,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1367,13 +1387,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1381,13 +1401,13 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1395,13 +1415,13 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1409,13 +1429,13 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1423,13 +1443,13 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1437,13 +1457,13 @@
         <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1451,13 +1471,13 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1465,13 +1485,13 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1479,13 +1499,13 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" t="s">
         <v>112</v>
-      </c>
-      <c r="C37" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" t="s">
-        <v>114</v>
       </c>
       <c r="E37" t="s">
         <v>18</v>
@@ -1496,13 +1516,13 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" t="s">
         <v>113</v>
-      </c>
-      <c r="C38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" t="s">
-        <v>115</v>
       </c>
       <c r="E38" t="s">
         <v>18</v>
@@ -1513,13 +1533,13 @@
         <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -1530,13 +1550,13 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -1547,10 +1567,10 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
         <v>21</v>
@@ -1564,13 +1584,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E42" t="s">
         <v>24</v>
@@ -1581,13 +1601,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -1598,13 +1618,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
@@ -1615,13 +1635,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
@@ -1632,13 +1652,13 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1646,13 +1666,13 @@
         <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1660,13 +1680,13 @@
         <v>26</v>
       </c>
       <c r="B48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
         <v>132</v>
-      </c>
-      <c r="C48" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1674,13 +1694,13 @@
         <v>26</v>
       </c>
       <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
         <v>133</v>
-      </c>
-      <c r="C49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1688,13 +1708,13 @@
         <v>26</v>
       </c>
       <c r="B50" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" t="s">
         <v>136</v>
-      </c>
-      <c r="C50" t="s">
-        <v>52</v>
-      </c>
-      <c r="D50" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1702,13 +1722,13 @@
         <v>26</v>
       </c>
       <c r="B51" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" t="s">
         <v>137</v>
-      </c>
-      <c r="C51" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1716,13 +1736,13 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1733,10 +1753,10 @@
         <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1744,13 +1764,13 @@
         <v>26</v>
       </c>
       <c r="B54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" t="s">
         <v>144</v>
-      </c>
-      <c r="C54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D54" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1758,13 +1778,13 @@
         <v>26</v>
       </c>
       <c r="B55" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" t="s">
         <v>145</v>
-      </c>
-      <c r="C55" t="s">
-        <v>52</v>
-      </c>
-      <c r="D55" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,10 +1795,10 @@
         <v>43</v>
       </c>
       <c r="C56" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1786,13 +1806,13 @@
         <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1800,13 +1820,13 @@
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1814,13 +1834,13 @@
         <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1828,13 +1848,13 @@
         <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C60" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1842,13 +1862,13 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1856,13 +1876,13 @@
         <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1873,13 +1893,13 @@
         <v>44</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D63" t="s">
         <v>21</v>
       </c>
       <c r="E63" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1890,13 +1910,13 @@
         <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D64" t="s">
         <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,10 +1927,10 @@
         <v>46</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1918,13 +1938,13 @@
         <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="C66" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1932,13 +1952,13 @@
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E67" t="s">
         <v>18</v>
@@ -1949,13 +1969,13 @@
         <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="C68" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E68" t="s">
         <v>18</v>
@@ -1966,13 +1986,13 @@
         <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>175</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D69" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
         <v>31</v>
@@ -1983,13 +2003,13 @@
         <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E70" t="s">
         <v>31</v>
@@ -2000,13 +2020,13 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="C71" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -2018,13 +2038,13 @@
         <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -2036,13 +2056,13 @@
         <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>178</v>
       </c>
       <c r="C73" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -2054,13 +2074,13 @@
         <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="C74" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>34</v>
@@ -2072,13 +2092,13 @@
         <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C75" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>34</v>
@@ -2090,13 +2110,13 @@
         <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C76" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>34</v>

--- a/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
+++ b/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C15N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81185DA9-D603-45A1-8190-C06A85922219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBCF669-9599-49A5-AA0E-03BC2D917562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
@@ -179,9 +179,6 @@
     <t>T36_meval_tissue</t>
   </si>
   <si>
-    <t>T37_phe</t>
-  </si>
-  <si>
     <t>T40_meval_C2</t>
   </si>
   <si>
@@ -582,6 +579,9 @@
   </si>
   <si>
     <t>T41_Ace2</t>
+  </si>
+  <si>
+    <t>T37_phe1</t>
   </si>
 </sst>
 </file>
@@ -989,13 +989,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1026,7 +1026,7 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -1040,7 +1040,7 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1051,13 +1051,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1065,13 +1065,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1079,13 +1079,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1093,13 +1093,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1107,13 +1107,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1121,13 +1121,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1135,13 +1135,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1149,13 +1149,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1163,13 +1163,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1177,13 +1177,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1194,7 +1194,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
@@ -1208,7 +1208,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1222,10 +1222,10 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1233,13 +1233,13 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1247,13 +1247,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1261,13 +1261,13 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1275,13 +1275,13 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1289,13 +1289,13 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1303,13 +1303,13 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,13 +1317,13 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" t="s">
         <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,13 +1331,13 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,13 +1345,13 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,13 +1359,13 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,13 +1373,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,13 +1387,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,13 +1401,13 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,13 +1415,13 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1429,13 +1429,13 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1443,13 +1443,13 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1457,13 +1457,13 @@
         <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1471,13 +1471,13 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1485,13 +1485,13 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1499,13 +1499,13 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E37" t="s">
         <v>18</v>
@@ -1516,13 +1516,13 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E38" t="s">
         <v>18</v>
@@ -1533,13 +1533,13 @@
         <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -1550,13 +1550,13 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -1567,10 +1567,10 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
         <v>21</v>
@@ -1584,13 +1584,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E42" t="s">
         <v>24</v>
@@ -1601,13 +1601,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
@@ -1635,13 +1635,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
@@ -1652,13 +1652,13 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1666,13 +1666,13 @@
         <v>26</v>
       </c>
       <c r="B47" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" t="s">
         <v>128</v>
-      </c>
-      <c r="C47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1680,13 +1680,13 @@
         <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1694,13 +1694,13 @@
         <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1708,13 +1708,13 @@
         <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1722,13 +1722,13 @@
         <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1736,13 +1736,13 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
+        <v>137</v>
+      </c>
+      <c r="C52" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" t="s">
         <v>138</v>
-      </c>
-      <c r="C52" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1753,10 +1753,10 @@
         <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1764,13 +1764,13 @@
         <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1778,13 +1778,13 @@
         <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1795,10 +1795,10 @@
         <v>43</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1806,13 +1806,13 @@
         <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1820,13 +1820,13 @@
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1834,13 +1834,13 @@
         <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1848,13 +1848,13 @@
         <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1862,13 +1862,13 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1876,13 +1876,13 @@
         <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1893,13 +1893,13 @@
         <v>44</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D63" t="s">
         <v>21</v>
       </c>
       <c r="E63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1910,13 +1910,13 @@
         <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D64" t="s">
         <v>21</v>
       </c>
       <c r="E64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,13 +1924,13 @@
         <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="C65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1938,13 +1938,13 @@
         <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1952,13 +1952,13 @@
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C67" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s">
         <v>18</v>
@@ -1969,13 +1969,13 @@
         <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E68" t="s">
         <v>18</v>
@@ -1986,13 +1986,13 @@
         <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
         <v>31</v>
@@ -2003,13 +2003,13 @@
         <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C70" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
         <v>31</v>
@@ -2020,13 +2020,13 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E71" t="s">
         <v>33</v>
@@ -2038,13 +2038,13 @@
         <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C72" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E72" t="s">
         <v>33</v>
@@ -2056,13 +2056,13 @@
         <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -2074,13 +2074,13 @@
         <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>34</v>
@@ -2092,13 +2092,13 @@
         <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C75" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>34</v>
@@ -2110,13 +2110,13 @@
         <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>34</v>

--- a/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
+++ b/jobs13C15N/diet_neg_all_13C15N_tracing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C15N\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBCF669-9599-49A5-AA0E-03BC2D917562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF592A17-090A-4BE6-9AF3-89900436F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="182">
   <si>
     <t>inclusion</t>
   </si>
@@ -582,6 +582,9 @@
   </si>
   <si>
     <t>T37_phe1</t>
+  </si>
+  <si>
+    <t>mzxml;neg;val-;M27</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1326,7 @@
         <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
